--- a/data/trans_camb/P68-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P68-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 10,44</t>
+          <t>-5,73; 11,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 20,04</t>
+          <t>1,43; 21,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 2,49</t>
+          <t>-15,95; 1,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 12,88</t>
+          <t>-8,51; 12,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 13,12</t>
+          <t>-11,44; 13,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 21,84</t>
+          <t>-5,42; 22,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 8,02</t>
+          <t>-5,29; 7,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 15,28</t>
+          <t>-1,39; 15,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 4,67</t>
+          <t>-9,64; 5,34</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 37,98</t>
+          <t>-18,01; 42,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 74,27</t>
+          <t>4,53; 82,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 10,15</t>
+          <t>-48,83; 7,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 64,85</t>
+          <t>-29,45; 61,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,94; 71,2</t>
+          <t>-40,65; 64,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 107,62</t>
+          <t>-20,84; 114,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 31,53</t>
+          <t>-16,95; 30,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 59,12</t>
+          <t>-5,27; 59,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 17,83</t>
+          <t>-32,78; 20,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 3,23</t>
+          <t>-4,81; 2,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 3,19</t>
+          <t>-4,64; 2,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,85; -2,68</t>
+          <t>-17,22; -2,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 7,5</t>
+          <t>-2,34; 7,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 2,99</t>
+          <t>-6,04; 2,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 13,79</t>
+          <t>-1,27; 13,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,17</t>
+          <t>-3,01; 3,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 1,46</t>
+          <t>-4,48; 1,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 1,47</t>
+          <t>-9,66; 1,41</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 14,26</t>
+          <t>-17,42; 10,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 13,4</t>
+          <t>-16,76; 12,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,88; -11,45</t>
+          <t>-60,69; -11,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 41,0</t>
+          <t>-10,17; 41,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 16,62</t>
+          <t>-26,58; 14,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 73,01</t>
+          <t>-5,69; 73,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 14,04</t>
+          <t>-12,15; 13,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 6,38</t>
+          <t>-17,68; 6,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,74; 6,32</t>
+          <t>-38,22; 5,82</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 2,12</t>
+          <t>-9,27; 2,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 6,11</t>
+          <t>-5,74; 5,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 3,04</t>
+          <t>-7,97; 2,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 5,03</t>
+          <t>-9,37; 4,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 8,45</t>
+          <t>-3,95; 9,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 4,3</t>
+          <t>-6,96; 5,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 1,63</t>
+          <t>-7,22; 2,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 5,73</t>
+          <t>-3,19; 5,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 2,26</t>
+          <t>-5,57; 2,29</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,63; 16,41</t>
+          <t>-44,41; 15,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 41,65</t>
+          <t>-27,76; 36,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 19,84</t>
+          <t>-37,58; 18,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,44; 27,05</t>
+          <t>-38,1; 26,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 44,75</t>
+          <t>-14,84; 52,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 25,25</t>
+          <t>-27,44; 27,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 9,44</t>
+          <t>-34,19; 14,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 32,23</t>
+          <t>-15,1; 32,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 13,86</t>
+          <t>-25,5; 12,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 1,27</t>
+          <t>-4,79; 1,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,76</t>
+          <t>-3,02; 3,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -3,79</t>
+          <t>-14,0; -3,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 4,68</t>
+          <t>-2,68; 5,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 3,27</t>
+          <t>-4,25; 2,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 8,85</t>
+          <t>-1,42; 8,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,82</t>
+          <t>-2,93; 1,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,64</t>
+          <t>-2,97; 2,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,55; -0,19</t>
+          <t>-8,51; -0,09</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 5,3</t>
+          <t>-18,07; 6,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 11,79</t>
+          <t>-11,49; 12,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -16,26</t>
+          <t>-54,56; -14,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 23,08</t>
+          <t>-11,44; 26,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 16,24</t>
+          <t>-18,15; 14,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 44,49</t>
+          <t>-6,66; 42,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 8,02</t>
+          <t>-11,7; 8,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 7,26</t>
+          <t>-11,89; 8,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,35; -0,89</t>
+          <t>-33,61; -0,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P68-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P68-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,56</t>
+          <t>-7,59</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,82</t>
+          <t>-4,25</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 11,29</t>
+          <t>-6,5; 10,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 21,53</t>
+          <t>0,75; 19,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 1,98</t>
+          <t>-15,44; 0,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 12,33</t>
+          <t>-8,03; 13,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 13,13</t>
+          <t>-11,91; 13,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 22,9</t>
+          <t>-8,2; 13,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 7,73</t>
+          <t>-4,89; 7,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 15,12</t>
+          <t>-1,06; 13,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 5,34</t>
+          <t>-10,64; 2,81</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-25,48%</t>
+          <t>-25,56%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-9,96%</t>
+          <t>-15,03%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 42,09</t>
+          <t>-20,13; 39,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 82,16</t>
+          <t>2,1; 72,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 7,99</t>
+          <t>-47,94; 3,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 61,65</t>
+          <t>-25,81; 70,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 64,39</t>
+          <t>-41,41; 62,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,84; 114,78</t>
+          <t>-29,11; 65,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 30,11</t>
+          <t>-15,74; 31,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 59,83</t>
+          <t>-3,47; 53,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,78; 20,0</t>
+          <t>-34,87; 11,88</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-8,15</t>
+          <t>-4,2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,2</t>
+          <t>3,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,07</t>
+          <t>-1,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 2,48</t>
+          <t>-5,24; 3,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,97</t>
+          <t>-4,85; 3,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,22; -2,65</t>
+          <t>-8,13; -0,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 7,1</t>
+          <t>-2,58; 7,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 2,72</t>
+          <t>-5,71; 3,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 13,52</t>
+          <t>-0,82; 7,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,08</t>
+          <t>-3,26; 3,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 1,39</t>
+          <t>-4,51; 1,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 1,41</t>
+          <t>-4,04; 1,71</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-31,63%</t>
+          <t>-16,28%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-12,82%</t>
+          <t>-5,9%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 10,11</t>
+          <t>-18,53; 12,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 12,4</t>
+          <t>-17,71; 13,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,69; -11,27</t>
+          <t>-28,59; -3,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 41,11</t>
+          <t>-11,44; 37,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 14,87</t>
+          <t>-25,02; 19,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 73,06</t>
+          <t>-3,41; 43,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 13,48</t>
+          <t>-12,87; 13,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 6,41</t>
+          <t>-17,6; 6,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 5,82</t>
+          <t>-15,95; 7,53</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,67</t>
+          <t>-2,27</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-1,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 2,38</t>
+          <t>-9,42; 1,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 5,68</t>
+          <t>-5,84; 6,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 2,83</t>
+          <t>-7,77; 3,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 4,98</t>
+          <t>-9,46; 5,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 9,42</t>
+          <t>-4,82; 9,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,02</t>
+          <t>-6,96; 3,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 2,31</t>
+          <t>-7,28; 1,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 5,8</t>
+          <t>-3,17; 5,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 2,29</t>
+          <t>-5,57; 2,43</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-14,6%</t>
+          <t>-12,39%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-5,34%</t>
+          <t>-5,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-8,31%</t>
+          <t>-7,35%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,41; 15,2</t>
+          <t>-45,27; 10,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 36,07</t>
+          <t>-27,84; 39,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,58; 18,87</t>
+          <t>-37,72; 22,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,1; 26,61</t>
+          <t>-37,21; 31,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 52,64</t>
+          <t>-19,42; 50,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 27,07</t>
+          <t>-27,64; 21,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 14,2</t>
+          <t>-33,76; 10,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 32,58</t>
+          <t>-14,29; 31,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 12,63</t>
+          <t>-24,97; 14,18</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,48</t>
+          <t>-4,74</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,28</t>
+          <t>-2,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,58</t>
+          <t>-4,54; 1,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 3,1</t>
+          <t>-3,25; 3,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,0; -3,6</t>
+          <t>-7,55; -1,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 5,25</t>
+          <t>-2,41; 4,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 2,98</t>
+          <t>-3,87; 3,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 8,62</t>
+          <t>-1,49; 4,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,83</t>
+          <t>-3,01; 1,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,05</t>
+          <t>-3,04; 1,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -0,09</t>
+          <t>-4,49; -0,28</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-29,98%</t>
+          <t>-19,02%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-13,82%</t>
+          <t>-9,62%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 6,66</t>
+          <t>-17,42; 7,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 12,84</t>
+          <t>-12,68; 12,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,56; -14,9</t>
+          <t>-28,45; -7,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 26,65</t>
+          <t>-10,51; 25,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 14,94</t>
+          <t>-16,58; 16,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 42,77</t>
+          <t>-6,27; 23,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 8,38</t>
+          <t>-12,19; 7,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 8,98</t>
+          <t>-12,08; 7,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,61; -0,36</t>
+          <t>-18,14; -1,22</t>
         </is>
       </c>
     </row>
